--- a/tame_output/ON/bt/strategyON_20231229.xlsx
+++ b/tame_output/ON/bt/strategyON_20231229.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>482.9%</t>
+          <t>483.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-134.0%</t>
+          <t>-133.9%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-37.8%</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.2%</t>
         </is>
       </c>
     </row>
@@ -43514,16 +43514,16 @@
         <v>3.1338083988329</v>
       </c>
       <c r="D1826" t="n">
-        <v>0.08417483617861027</v>
+        <v>0.08497935725618927</v>
       </c>
       <c r="E1826" t="n">
-        <v>3.167121908990598</v>
+        <v>3.167443717421629</v>
       </c>
       <c r="F1826" t="n">
-        <v>1.713369325536608</v>
+        <v>1.714173846614187</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.161829994154867</v>
+        <v>4.162312706801415</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231229.xlsx
+++ b/tame_output/ON/bt/strategyON_20231229.xlsx
@@ -43514,16 +43514,16 @@
         <v>3.1338083988329</v>
       </c>
       <c r="D1826" t="n">
-        <v>0.08497935725618927</v>
+        <v>0.08510182148354056</v>
       </c>
       <c r="E1826" t="n">
-        <v>3.167443717421629</v>
+        <v>3.16749270311257</v>
       </c>
       <c r="F1826" t="n">
-        <v>1.714173846614187</v>
+        <v>1.714296310841539</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.162312706801415</v>
+        <v>4.162386185337825</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231229.xlsx
+++ b/tame_output/ON/bt/strategyON_20231229.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>483.0%</t>
+          <t>480.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-133.9%</t>
+          <t>-141.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-28.6%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-45.0%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>106.3%</t>
+          <t>104.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
     </row>
@@ -43514,16 +43514,16 @@
         <v>3.1338083988329</v>
       </c>
       <c r="D1826" t="n">
-        <v>0.08510182148354056</v>
+        <v>0.01307931249243349</v>
       </c>
       <c r="E1826" t="n">
-        <v>3.16749270311257</v>
+        <v>3.138683699516127</v>
       </c>
       <c r="F1826" t="n">
-        <v>1.714296310841539</v>
+        <v>1.642273801850431</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.162386185337825</v>
+        <v>4.119172679943161</v>
       </c>
     </row>
   </sheetData>
